--- a/reports/historical_reports_KalmanTest.xlsx
+++ b/reports/historical_reports_KalmanTest.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="20260711-144728" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="20260711-161704" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="20260714-182450" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1083,7 +1084,6 @@
           <t>Annual volatility (Log Return)</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -1101,7 +1101,6 @@
           <t>Sharpe ratio (log returns)</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1139,7 +1138,6 @@
           <t>Stability</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1219,6 +1217,422 @@
       </c>
       <c r="B39" t="n">
         <v>62.86</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KalmanTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-12T10:23:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-07-14T10:23:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>-0.012344</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.896362</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.227249</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.228662</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>-10.151159</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-10.168392</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-6.984312</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-29.638494</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.030243</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.294009</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.9733579999999999</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-0.000836</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.809881</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>22.30605</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>55.15</v>
       </c>
     </row>
   </sheetData>

--- a/reports/historical_reports_KalmanTest.xlsx
+++ b/reports/historical_reports_KalmanTest.xlsx
@@ -10,6 +10,8 @@
     <sheet name="20260711-144728" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="20260711-161704" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="20260714-182450" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="20260715-171143" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="20260715-191959" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1638,4 +1640,860 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KalmanTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-06-15T10:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-15T10:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.046352</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.438667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.282329</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.285858</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-2.117525</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-2.223869</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-18.597102</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-6.990217</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.143057</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.524986</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.981289</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.005862</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.195366</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4.935949</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>65.12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KalmanTest</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>timeframe</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>1h</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>param.trade_usd</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>param.printlog</t>
+        </is>
+      </c>
+      <c r="B5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>param.diag</t>
+        </is>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>param.k</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>param.a</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>param.warmup</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>param.q_level</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>param.q_vel</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1e-07</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>param.reversion</t>
+        </is>
+      </c>
+      <c r="B12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>broker.starting_cash</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>broker.leverage</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>broker.commission</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0002</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>broker.commission_pct_per_side</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.0200%</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>risk_free_annual</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>window_start</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2025-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>window_end</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-07-15T11:59:59.999000</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>backtest_days</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>symbols</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B23" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Cumulative return</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>-0.187727</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Annualised return (CAGR)</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>-0.187727</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Return)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.258494</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Annual volatility (Log Return)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.258603</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (Returns)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>-0.907313</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sharpe ratio (log returns)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>-1.029332</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sortino ratio</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>-1.181231</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Calmar ratio</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>-0.486369</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Max drawdown</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-0.385977</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Stability</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.002336</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Tail ratio</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.901181</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Daily VaR (5%)</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.004376</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>Skew</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1.834145</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>Kurtosis</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>32.90128</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Total trades</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>Winning trades</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>Losing trades</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>Win rate %</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>61.66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>